--- a/nriss-patch-2/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:58:47+00:00</t>
+    <t>2026-08-04T07:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-2/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:44:41+00:00</t>
+    <t>2026-08-07T09:15:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -23980,7 +23980,7 @@
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G180" t="s" s="2">
         <v>80</v>
